--- a/data/availability/projects/palm-hills-developments/hacienda-bay.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-bay.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Hacienda Bay</t>
+          <t>Live inventory for hacienda-bay</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,56 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hacienda-bay</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>357</v>
+      </c>
+      <c r="F2" t="n">
+        <v>357</v>
+      </c>
+      <c r="G2" t="n">
+        <v>141.35</v>
+      </c>
+      <c r="H2" t="n">
+        <v>141.35</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Hacienda Bay (1)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +674,63 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>hacienda-bay</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Hacienda Bay (1)</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>357</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>141346000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/palm-hills-developments/hacienda-bay.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-bay.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for hacienda-bay</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -709,7 +719,6 @@
       <c r="G2" t="n">
         <v>357.59</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>

--- a/data/availability/projects/palm-hills-developments/hacienda-bay.xlsx
+++ b/data/availability/projects/palm-hills-developments/hacienda-bay.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -597,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
